--- a/compare/output/dscale_RenTES_downscaled_SSP434.xlsx
+++ b/compare/output/dscale_RenTES_downscaled_SSP434.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>449447.744417</v>
+        <v>448822.192793</v>
       </c>
       <c r="F2" t="n">
-        <v>464320.648406</v>
+        <v>462822.760238</v>
       </c>
       <c r="G2" t="n">
-        <v>525244.183613</v>
+        <v>522070.43879</v>
       </c>
       <c r="H2" t="n">
-        <v>585442.831975</v>
+        <v>578901.6177450001</v>
       </c>
       <c r="I2" t="n">
-        <v>613367.187526</v>
+        <v>598464.747748</v>
       </c>
       <c r="J2" t="n">
         <v>127181.736005</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>38589.329551</v>
+        <v>38541.176485</v>
       </c>
       <c r="F3" t="n">
-        <v>34648.658948</v>
+        <v>34550.894594</v>
       </c>
       <c r="G3" t="n">
-        <v>35269.940392</v>
+        <v>35087.287576</v>
       </c>
       <c r="H3" t="n">
-        <v>36825.174262</v>
+        <v>36479.09241</v>
       </c>
       <c r="I3" t="n">
-        <v>37744.664297</v>
+        <v>36989.255181</v>
       </c>
       <c r="J3" t="n">
         <v>13974.878673</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44912.998158</v>
+        <v>44866.639574</v>
       </c>
       <c r="F4" t="n">
-        <v>37537.208483</v>
+        <v>37452.560477</v>
       </c>
       <c r="G4" t="n">
-        <v>34566.441832</v>
+        <v>34429.634818</v>
       </c>
       <c r="H4" t="n">
-        <v>33638.614832</v>
+        <v>33405.614109</v>
       </c>
       <c r="I4" t="n">
-        <v>33270.520527</v>
+        <v>32794.763566</v>
       </c>
       <c r="J4" t="n">
         <v>18744.951841</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21891.179854</v>
+        <v>21958.120259</v>
       </c>
       <c r="F5" t="n">
-        <v>27150.862532</v>
+        <v>27316.460052</v>
       </c>
       <c r="G5" t="n">
-        <v>39436.701346</v>
+        <v>39792.707392</v>
       </c>
       <c r="H5" t="n">
-        <v>54643.403038</v>
+        <v>55388.24691</v>
       </c>
       <c r="I5" t="n">
-        <v>72473.930806</v>
+        <v>74219.785466</v>
       </c>
       <c r="J5" t="n">
         <v>154403.379207</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1151809.987412</v>
+        <v>1151733.738251</v>
       </c>
       <c r="F6" t="n">
-        <v>1192665.632396</v>
+        <v>1192469.103228</v>
       </c>
       <c r="G6" t="n">
-        <v>1249926.941</v>
+        <v>1249840.755176</v>
       </c>
       <c r="H6" t="n">
-        <v>1331679.529805</v>
+        <v>1332115.655067</v>
       </c>
       <c r="I6" t="n">
-        <v>1443862.80275</v>
+        <v>1445763.002394</v>
       </c>
       <c r="J6" t="n">
         <v>1699248.884028</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>644985.097648</v>
+        <v>645033.5574310001</v>
       </c>
       <c r="F7" t="n">
-        <v>689627.855549</v>
+        <v>689700.632799</v>
       </c>
       <c r="G7" t="n">
-        <v>834760.782717</v>
+        <v>834681.613185</v>
       </c>
       <c r="H7" t="n">
-        <v>1015842.626951</v>
+        <v>1015220.379051</v>
       </c>
       <c r="I7" t="n">
-        <v>1211623.409095</v>
+        <v>1209191.407063</v>
       </c>
       <c r="J7" t="n">
         <v>1326457.617226</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>190151.372137</v>
+        <v>190284.846894</v>
       </c>
       <c r="F8" t="n">
-        <v>201750.798174</v>
+        <v>202073.48537</v>
       </c>
       <c r="G8" t="n">
-        <v>239834.155498</v>
+        <v>240498.282669</v>
       </c>
       <c r="H8" t="n">
-        <v>287799.246593</v>
+        <v>289162.308751</v>
       </c>
       <c r="I8" t="n">
-        <v>344155.674845</v>
+        <v>347331.103063</v>
       </c>
       <c r="J8" t="n">
         <v>526127.728794</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8370.849187</v>
+        <v>8443.2986</v>
       </c>
       <c r="F9" t="n">
-        <v>7117.323968</v>
+        <v>7264.501905</v>
       </c>
       <c r="G9" t="n">
-        <v>6732.130874</v>
+        <v>6992.031136</v>
       </c>
       <c r="H9" t="n">
-        <v>7065.967275</v>
+        <v>7527.976619</v>
       </c>
       <c r="I9" t="n">
-        <v>9010.406371999999</v>
+        <v>9957.306811</v>
       </c>
       <c r="J9" t="n">
         <v>41684.150447</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>120680.603147</v>
+        <v>120755.714513</v>
       </c>
       <c r="F10" t="n">
-        <v>112818.863799</v>
+        <v>113016.241944</v>
       </c>
       <c r="G10" t="n">
-        <v>112942.559459</v>
+        <v>113382.10488</v>
       </c>
       <c r="H10" t="n">
-        <v>120182.173911</v>
+        <v>121125.395133</v>
       </c>
       <c r="I10" t="n">
-        <v>134173.506793</v>
+        <v>136433.514531</v>
       </c>
       <c r="J10" t="n">
         <v>238205.356587</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>387028.432077</v>
+        <v>387995.592876</v>
       </c>
       <c r="F11" t="n">
-        <v>391577.443564</v>
+        <v>393854.993793</v>
       </c>
       <c r="G11" t="n">
-        <v>440280.367458</v>
+        <v>444966.980749</v>
       </c>
       <c r="H11" t="n">
-        <v>514606.199774</v>
+        <v>524210.115917</v>
       </c>
       <c r="I11" t="n">
-        <v>627661.835554</v>
+        <v>649883.565629</v>
       </c>
       <c r="J11" t="n">
         <v>1547699.078167</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>483643.186958</v>
+        <v>482986.717913</v>
       </c>
       <c r="F12" t="n">
-        <v>505648.489047</v>
+        <v>504052.223317</v>
       </c>
       <c r="G12" t="n">
-        <v>591367.3969000001</v>
+        <v>587856.9597060001</v>
       </c>
       <c r="H12" t="n">
-        <v>695045.766062</v>
+        <v>687384.97992</v>
       </c>
       <c r="I12" t="n">
-        <v>769485.079948</v>
+        <v>750974.440802</v>
       </c>
       <c r="J12" t="n">
         <v>172446.891746</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>512742.870453</v>
+        <v>512832.055411</v>
       </c>
       <c r="F13" t="n">
-        <v>517617.538262</v>
+        <v>517907.465415</v>
       </c>
       <c r="G13" t="n">
-        <v>567541.7388770001</v>
+        <v>568304.54389</v>
       </c>
       <c r="H13" t="n">
-        <v>648170.146864</v>
+        <v>650020.2997110001</v>
       </c>
       <c r="I13" t="n">
-        <v>758942.174531</v>
+        <v>763768.300787</v>
       </c>
       <c r="J13" t="n">
         <v>1101223.376191</v>
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1098.21476</v>
+        <v>1097.665708</v>
       </c>
       <c r="F14" t="n">
-        <v>1270.220428</v>
+        <v>1268.617428</v>
       </c>
       <c r="G14" t="n">
-        <v>2417.916765</v>
+        <v>2411.705034</v>
       </c>
       <c r="H14" t="n">
-        <v>4316.931261</v>
+        <v>4294.153318</v>
       </c>
       <c r="I14" t="n">
-        <v>7585.58882</v>
+        <v>7483.75813</v>
       </c>
       <c r="J14" t="n">
         <v>777873.639335</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>203617.435462</v>
+        <v>203617.833967</v>
       </c>
       <c r="F15" t="n">
-        <v>259429.299319</v>
+        <v>259430.297475</v>
       </c>
       <c r="G15" t="n">
-        <v>515760.639671</v>
+        <v>515763.992245</v>
       </c>
       <c r="H15" t="n">
-        <v>930305.769155</v>
+        <v>930317.160237</v>
       </c>
       <c r="I15" t="n">
-        <v>1592890.12026</v>
+        <v>1592939.928716</v>
       </c>
       <c r="J15" t="n">
         <v>1952956.069712</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>25203.077773</v>
+        <v>25202.713456</v>
       </c>
       <c r="F16" t="n">
-        <v>25613.106074</v>
+        <v>25612.267594</v>
       </c>
       <c r="G16" t="n">
-        <v>41405.670896</v>
+        <v>41403.266615</v>
       </c>
       <c r="H16" t="n">
-        <v>64676.169412</v>
+        <v>64669.26133</v>
       </c>
       <c r="I16" t="n">
-        <v>101317.516126</v>
+        <v>101291.665379</v>
       </c>
       <c r="J16" t="n">
         <v>313322.356838</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73241.48386199999</v>
+        <v>73241.82399200001</v>
       </c>
       <c r="F17" t="n">
-        <v>84017.484251</v>
+        <v>84018.436391</v>
       </c>
       <c r="G17" t="n">
-        <v>153044.754684</v>
+        <v>153048.22308</v>
       </c>
       <c r="H17" t="n">
-        <v>256909.740638</v>
+        <v>256921.738238</v>
       </c>
       <c r="I17" t="n">
-        <v>413062.12496</v>
+        <v>413112.785022</v>
       </c>
       <c r="J17" t="n">
         <v>207682.077219</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>51164.029543</v>
+        <v>51164.204276</v>
       </c>
       <c r="F18" t="n">
-        <v>63638.076196</v>
+        <v>63638.56738</v>
       </c>
       <c r="G18" t="n">
-        <v>119768.241804</v>
+        <v>119770.036846</v>
       </c>
       <c r="H18" t="n">
-        <v>206842.178142</v>
+        <v>206848.475484</v>
       </c>
       <c r="I18" t="n">
-        <v>347472.667883</v>
+        <v>347499.880801</v>
       </c>
       <c r="J18" t="n">
         <v>314873.613448</v>
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>225316.352913</v>
+        <v>225845.935763</v>
       </c>
       <c r="F19" t="n">
-        <v>239008.798</v>
+        <v>240327.659526</v>
       </c>
       <c r="G19" t="n">
-        <v>261390.10403</v>
+        <v>264129.338547</v>
       </c>
       <c r="H19" t="n">
-        <v>287904.574389</v>
+        <v>293462.998981</v>
       </c>
       <c r="I19" t="n">
-        <v>339051.482209</v>
+        <v>352225.501793</v>
       </c>
       <c r="J19" t="n">
         <v>920341.866924</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>21490.699983</v>
+        <v>21576.13407</v>
       </c>
       <c r="F20" t="n">
-        <v>22133.165168</v>
+        <v>22326.020556</v>
       </c>
       <c r="G20" t="n">
-        <v>24441.862574</v>
+        <v>24805.675288</v>
       </c>
       <c r="H20" t="n">
-        <v>26522.970564</v>
+        <v>27190.051736</v>
       </c>
       <c r="I20" t="n">
-        <v>30303.917897</v>
+        <v>31736.301714</v>
       </c>
       <c r="J20" t="n">
         <v>85142.750874</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>98889.979372</v>
+        <v>98779.727436</v>
       </c>
       <c r="F21" t="n">
-        <v>82286.378903</v>
+        <v>82082.536744</v>
       </c>
       <c r="G21" t="n">
-        <v>73394.105708</v>
+        <v>73068.72278</v>
       </c>
       <c r="H21" t="n">
-        <v>68393.475179</v>
+        <v>67859.210043</v>
       </c>
       <c r="I21" t="n">
-        <v>66016.124765</v>
+        <v>64947.94623</v>
       </c>
       <c r="J21" t="n">
         <v>29107.06583</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>247767.561957</v>
+        <v>247866.1036</v>
       </c>
       <c r="F22" t="n">
-        <v>263564.126925</v>
+        <v>263791.287331</v>
       </c>
       <c r="G22" t="n">
-        <v>284547.365653</v>
+        <v>285008.248988</v>
       </c>
       <c r="H22" t="n">
-        <v>303008.626156</v>
+        <v>303982.234052</v>
       </c>
       <c r="I22" t="n">
-        <v>329137.708729</v>
+        <v>331590.184375</v>
       </c>
       <c r="J22" t="n">
         <v>462687.071943</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>757134.603346</v>
+        <v>756204.4286709999</v>
       </c>
       <c r="F23" t="n">
-        <v>853052.045642</v>
+        <v>850612.7050280001</v>
       </c>
       <c r="G23" t="n">
-        <v>994272.0400189999</v>
+        <v>988965.617717</v>
       </c>
       <c r="H23" t="n">
-        <v>1151782.33093</v>
+        <v>1140576.721348</v>
       </c>
       <c r="I23" t="n">
-        <v>1320033.932958</v>
+        <v>1292578.794389</v>
       </c>
       <c r="J23" t="n">
         <v>400812.426055</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>11638.369157</v>
+        <v>11723.713908</v>
       </c>
       <c r="F24" t="n">
-        <v>11878.029092</v>
+        <v>12074.537272</v>
       </c>
       <c r="G24" t="n">
-        <v>13027.758912</v>
+        <v>13407.941182</v>
       </c>
       <c r="H24" t="n">
-        <v>14667.538881</v>
+        <v>15387.094762</v>
       </c>
       <c r="I24" t="n">
-        <v>18697.986877</v>
+        <v>20293.525903</v>
       </c>
       <c r="J24" t="n">
         <v>82196.798114</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>23676.438627</v>
+        <v>23682.644025</v>
       </c>
       <c r="F25" t="n">
-        <v>21020.959001</v>
+        <v>21038.916569</v>
       </c>
       <c r="G25" t="n">
-        <v>20066.968372</v>
+        <v>20105.186521</v>
       </c>
       <c r="H25" t="n">
-        <v>19826.122859</v>
+        <v>19902.844223</v>
       </c>
       <c r="I25" t="n">
-        <v>20593.022411</v>
+        <v>20771.939488</v>
       </c>
       <c r="J25" t="n">
         <v>28642.698415</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>529423.28237</v>
+        <v>529743.308889</v>
       </c>
       <c r="F26" t="n">
-        <v>536620.605293</v>
+        <v>537464.337391</v>
       </c>
       <c r="G26" t="n">
-        <v>549358.126532</v>
+        <v>551236.412172</v>
       </c>
       <c r="H26" t="n">
-        <v>570664.1789769999</v>
+        <v>574726.3276899999</v>
       </c>
       <c r="I26" t="n">
-        <v>623893.992062</v>
+        <v>634081.773142</v>
       </c>
       <c r="J26" t="n">
         <v>1118713.684794</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>287447.540594</v>
+        <v>287420.10817</v>
       </c>
       <c r="F27" t="n">
-        <v>298033.093875</v>
+        <v>297998.057499</v>
       </c>
       <c r="G27" t="n">
-        <v>308744.909816</v>
+        <v>308781.344542</v>
       </c>
       <c r="H27" t="n">
-        <v>322127.595009</v>
+        <v>322417.172424</v>
       </c>
       <c r="I27" t="n">
-        <v>349741.564446</v>
+        <v>350876.231129</v>
       </c>
       <c r="J27" t="n">
         <v>448412.198432</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>95676.84987999999</v>
+        <v>95619.573668</v>
       </c>
       <c r="F28" t="n">
-        <v>88800.51525700001</v>
+        <v>88681.65923999999</v>
       </c>
       <c r="G28" t="n">
-        <v>97966.09372</v>
+        <v>97700.84759999999</v>
       </c>
       <c r="H28" t="n">
-        <v>112320.573229</v>
+        <v>111713.330914</v>
       </c>
       <c r="I28" t="n">
-        <v>131298.115297</v>
+        <v>129665.649489</v>
       </c>
       <c r="J28" t="n">
         <v>81432.86300300001</v>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>143000.863185</v>
+        <v>143224.613231</v>
       </c>
       <c r="F29" t="n">
-        <v>129925.941769</v>
+        <v>130625.921407</v>
       </c>
       <c r="G29" t="n">
-        <v>128271.004111</v>
+        <v>129844.043468</v>
       </c>
       <c r="H29" t="n">
-        <v>134840.207089</v>
+        <v>137837.685388</v>
       </c>
       <c r="I29" t="n">
-        <v>159825.732442</v>
+        <v>165127.147344</v>
       </c>
       <c r="J29" t="n">
         <v>257887.642139</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>238612.409656</v>
+        <v>239059.717185</v>
       </c>
       <c r="F30" t="n">
-        <v>179085.689146</v>
+        <v>180850.586329</v>
       </c>
       <c r="G30" t="n">
-        <v>151132.5608</v>
+        <v>155034.573595</v>
       </c>
       <c r="H30" t="n">
-        <v>153630.372662</v>
+        <v>160660.098835</v>
       </c>
       <c r="I30" t="n">
-        <v>198203.002743</v>
+        <v>210270.238443</v>
       </c>
       <c r="J30" t="n">
         <v>411281.815927</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>394945.75766</v>
+        <v>392097.152546</v>
       </c>
       <c r="F31" t="n">
-        <v>328146.168006</v>
+        <v>323461.628495</v>
       </c>
       <c r="G31" t="n">
-        <v>278218.190041</v>
+        <v>272388.458606</v>
       </c>
       <c r="H31" t="n">
-        <v>244957.447813</v>
+        <v>237694.797906</v>
       </c>
       <c r="I31" t="n">
-        <v>215146.072235</v>
+        <v>205380.158255</v>
       </c>
       <c r="J31" t="n">
         <v>88784.42891</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>365164.516759</v>
+        <v>365208.824703</v>
       </c>
       <c r="F32" t="n">
-        <v>292693.624416</v>
+        <v>293719.3897</v>
       </c>
       <c r="G32" t="n">
-        <v>256166.587693</v>
+        <v>259103.808721</v>
       </c>
       <c r="H32" t="n">
-        <v>249833.429515</v>
+        <v>255571.99944</v>
       </c>
       <c r="I32" t="n">
-        <v>285349.868409</v>
+        <v>295314.028175</v>
       </c>
       <c r="J32" t="n">
         <v>457603.626971</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>380391.869885</v>
+        <v>380656.440092</v>
       </c>
       <c r="F33" t="n">
-        <v>331447.790014</v>
+        <v>332643.696784</v>
       </c>
       <c r="G33" t="n">
-        <v>311681.512926</v>
+        <v>314709.652441</v>
       </c>
       <c r="H33" t="n">
-        <v>314073.082602</v>
+        <v>319985.255783</v>
       </c>
       <c r="I33" t="n">
-        <v>356592.240874</v>
+        <v>367004.087227</v>
       </c>
       <c r="J33" t="n">
         <v>540456.81443</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1581979.157773</v>
+        <v>1576602.760893</v>
       </c>
       <c r="F34" t="n">
-        <v>2331552.588974</v>
+        <v>2309788.648698</v>
       </c>
       <c r="G34" t="n">
-        <v>3465146.810886</v>
+        <v>3407078.338029</v>
       </c>
       <c r="H34" t="n">
-        <v>4486110.840486</v>
+        <v>4366815.751395</v>
       </c>
       <c r="I34" t="n">
-        <v>5037621.445937</v>
+        <v>4816834.262775</v>
       </c>
       <c r="J34" t="n">
         <v>2334224.227828</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>92248.622162</v>
+        <v>92266.615637</v>
       </c>
       <c r="F35" t="n">
-        <v>98651.087616</v>
+        <v>98640.99810300001</v>
       </c>
       <c r="G35" t="n">
-        <v>109781.411825</v>
+        <v>109799.684858</v>
       </c>
       <c r="H35" t="n">
-        <v>118675.184605</v>
+        <v>118917.572844</v>
       </c>
       <c r="I35" t="n">
-        <v>130155.621393</v>
+        <v>130916.410583</v>
       </c>
       <c r="J35" t="n">
         <v>154512.211511</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>42053.472994</v>
+        <v>41793.155144</v>
       </c>
       <c r="F36" t="n">
-        <v>35647.702464</v>
+        <v>35211.335371</v>
       </c>
       <c r="G36" t="n">
-        <v>28353.285936</v>
+        <v>27867.148221</v>
       </c>
       <c r="H36" t="n">
-        <v>22457.517557</v>
+        <v>21958.284421</v>
       </c>
       <c r="I36" t="n">
-        <v>18207.469463</v>
+        <v>17665.090026</v>
       </c>
       <c r="J36" t="n">
         <v>10771.307147</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>217488.825198</v>
+        <v>215999.902273</v>
       </c>
       <c r="F37" t="n">
-        <v>160558.841908</v>
+        <v>158465.44716</v>
       </c>
       <c r="G37" t="n">
-        <v>125423.809188</v>
+        <v>123151.018576</v>
       </c>
       <c r="H37" t="n">
-        <v>103637.557079</v>
+        <v>101168.395292</v>
       </c>
       <c r="I37" t="n">
-        <v>88893.94343299999</v>
+        <v>85949.41405399999</v>
       </c>
       <c r="J37" t="n">
         <v>51421.428172</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>245326.805091</v>
+        <v>247383.83549</v>
       </c>
       <c r="F38" t="n">
-        <v>232673.39836</v>
+        <v>237024.035691</v>
       </c>
       <c r="G38" t="n">
-        <v>231370.612493</v>
+        <v>239092.103697</v>
       </c>
       <c r="H38" t="n">
-        <v>253802.779843</v>
+        <v>266657.59056</v>
       </c>
       <c r="I38" t="n">
-        <v>334768.883075</v>
+        <v>355952.2614</v>
       </c>
       <c r="J38" t="n">
         <v>693181.707834</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>897454.594617</v>
+        <v>891042.6331879999</v>
       </c>
       <c r="F39" t="n">
-        <v>687939.046609</v>
+        <v>678382.116646</v>
       </c>
       <c r="G39" t="n">
-        <v>569675.070349</v>
+        <v>558211.218446</v>
       </c>
       <c r="H39" t="n">
-        <v>497924.530041</v>
+        <v>483935.85099</v>
       </c>
       <c r="I39" t="n">
-        <v>441216.891219</v>
+        <v>422488.090766</v>
       </c>
       <c r="J39" t="n">
         <v>200359.842573</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>136842.420683</v>
+        <v>135877.760129</v>
       </c>
       <c r="F40" t="n">
-        <v>114903.035135</v>
+        <v>113302.816046</v>
       </c>
       <c r="G40" t="n">
-        <v>100161.929544</v>
+        <v>98111.78405</v>
       </c>
       <c r="H40" t="n">
-        <v>88168.409216</v>
+        <v>85630.457788</v>
       </c>
       <c r="I40" t="n">
-        <v>77544.08739</v>
+        <v>74158.179474</v>
       </c>
       <c r="J40" t="n">
         <v>33774.483628</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>161319.219577</v>
+        <v>160232.265253</v>
       </c>
       <c r="F41" t="n">
-        <v>151555.916827</v>
+        <v>149512.383043</v>
       </c>
       <c r="G41" t="n">
-        <v>137883.858598</v>
+        <v>135160.548908</v>
       </c>
       <c r="H41" t="n">
-        <v>125111.266525</v>
+        <v>121663.459998</v>
       </c>
       <c r="I41" t="n">
-        <v>112219.492859</v>
+        <v>107606.770754</v>
       </c>
       <c r="J41" t="n">
         <v>53989.654008</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>9445.383239000001</v>
+        <v>9619.225649</v>
       </c>
       <c r="F42" t="n">
-        <v>8960.300804</v>
+        <v>9316.748169</v>
       </c>
       <c r="G42" t="n">
-        <v>9408.429029999999</v>
+        <v>10005.469585</v>
       </c>
       <c r="H42" t="n">
-        <v>11113.818385</v>
+        <v>12064.216121</v>
       </c>
       <c r="I42" t="n">
-        <v>16277.188756</v>
+        <v>17792.619264</v>
       </c>
       <c r="J42" t="n">
         <v>40258.743589</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>397851.831105</v>
+        <v>394921.259827</v>
       </c>
       <c r="F43" t="n">
-        <v>448883.485186</v>
+        <v>442085.211592</v>
       </c>
       <c r="G43" t="n">
-        <v>502721.976627</v>
+        <v>490968.768701</v>
       </c>
       <c r="H43" t="n">
-        <v>540835.323297</v>
+        <v>521942.487044</v>
       </c>
       <c r="I43" t="n">
-        <v>536193.410314</v>
+        <v>505465.899117</v>
       </c>
       <c r="J43" t="n">
         <v>136542.218127</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>190166.390357</v>
+        <v>191078.731345</v>
       </c>
       <c r="F44" t="n">
-        <v>183998.773392</v>
+        <v>186117.474581</v>
       </c>
       <c r="G44" t="n">
-        <v>189608.256885</v>
+        <v>193695.569784</v>
       </c>
       <c r="H44" t="n">
-        <v>211202.371897</v>
+        <v>218446.117125</v>
       </c>
       <c r="I44" t="n">
-        <v>270270.994877</v>
+        <v>282730.52755</v>
       </c>
       <c r="J44" t="n">
         <v>497927.372151</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>38954.296432</v>
+        <v>39251.146614</v>
       </c>
       <c r="F45" t="n">
-        <v>38388.639492</v>
+        <v>39006.83412</v>
       </c>
       <c r="G45" t="n">
-        <v>39246.15732</v>
+        <v>40343.371528</v>
       </c>
       <c r="H45" t="n">
-        <v>42654.231791</v>
+        <v>44490.700104</v>
       </c>
       <c r="I45" t="n">
-        <v>54070.001235</v>
+        <v>57093.648667</v>
       </c>
       <c r="J45" t="n">
         <v>104292.866565</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>131647.452947</v>
+        <v>132717.609568</v>
       </c>
       <c r="F46" t="n">
-        <v>128264.03899</v>
+        <v>130745.019202</v>
       </c>
       <c r="G46" t="n">
-        <v>139084.38293</v>
+        <v>143817.910727</v>
       </c>
       <c r="H46" t="n">
-        <v>168635.178762</v>
+        <v>177126.228969</v>
       </c>
       <c r="I46" t="n">
-        <v>248440.536158</v>
+        <v>263532.816156</v>
       </c>
       <c r="J46" t="n">
         <v>556653.974944</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1664297.285285</v>
+        <v>1682494.792933</v>
       </c>
       <c r="F47" t="n">
-        <v>1801167.293803</v>
+        <v>1838522.052602</v>
       </c>
       <c r="G47" t="n">
-        <v>1943402.805162</v>
+        <v>2009716.698403</v>
       </c>
       <c r="H47" t="n">
-        <v>2243810.015119</v>
+        <v>2356753.609889</v>
       </c>
       <c r="I47" t="n">
-        <v>3066924.119864</v>
+        <v>3258751.403705</v>
       </c>
       <c r="J47" t="n">
         <v>6525561.245358</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>99458.137694</v>
+        <v>100823.668711</v>
       </c>
       <c r="F48" t="n">
-        <v>96078.24502</v>
+        <v>98937.72158899999</v>
       </c>
       <c r="G48" t="n">
-        <v>100825.503878</v>
+        <v>105760.913855</v>
       </c>
       <c r="H48" t="n">
-        <v>116762.623699</v>
+        <v>124849.845504</v>
       </c>
       <c r="I48" t="n">
-        <v>164326.835506</v>
+        <v>177559.945663</v>
       </c>
       <c r="J48" t="n">
         <v>381909.395102</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>540422.694714</v>
+        <v>536633.662417</v>
       </c>
       <c r="F49" t="n">
-        <v>490460.795724</v>
+        <v>483588.303475</v>
       </c>
       <c r="G49" t="n">
-        <v>444604.471089</v>
+        <v>435386.401525</v>
       </c>
       <c r="H49" t="n">
-        <v>401484.662674</v>
+        <v>389708.917982</v>
       </c>
       <c r="I49" t="n">
-        <v>354549.239682</v>
+        <v>338767.469352</v>
       </c>
       <c r="J49" t="n">
         <v>152173.83888</v>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>14450.045383</v>
+        <v>14353.394564</v>
       </c>
       <c r="F50" t="n">
-        <v>12307.170755</v>
+        <v>12144.194456</v>
       </c>
       <c r="G50" t="n">
-        <v>10276.730588</v>
+        <v>10080.507234</v>
       </c>
       <c r="H50" t="n">
-        <v>8612.299429999999</v>
+        <v>8388.298011000001</v>
       </c>
       <c r="I50" t="n">
-        <v>7248.0288</v>
+        <v>6976.349396</v>
       </c>
       <c r="J50" t="n">
         <v>3692.773554</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>151153.174872</v>
+        <v>151819.7968</v>
       </c>
       <c r="F51" t="n">
-        <v>132418.19177</v>
+        <v>134064.498402</v>
       </c>
       <c r="G51" t="n">
-        <v>127039.656356</v>
+        <v>130237.392103</v>
       </c>
       <c r="H51" t="n">
-        <v>134756.306817</v>
+        <v>140361.402213</v>
       </c>
       <c r="I51" t="n">
-        <v>170627.69692</v>
+        <v>180138.999937</v>
       </c>
       <c r="J51" t="n">
         <v>333851.429185</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>151398.517731</v>
+        <v>150914.780809</v>
       </c>
       <c r="F52" t="n">
-        <v>114932.685051</v>
+        <v>114483.389572</v>
       </c>
       <c r="G52" t="n">
-        <v>94718.26141599999</v>
+        <v>94637.89061</v>
       </c>
       <c r="H52" t="n">
-        <v>86007.551148</v>
+        <v>86467.98445</v>
       </c>
       <c r="I52" t="n">
-        <v>88712.714057</v>
+        <v>89909.699559</v>
       </c>
       <c r="J52" t="n">
         <v>112923.690483</v>
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>251795.822672</v>
+        <v>251795.759349</v>
       </c>
       <c r="F54" t="n">
-        <v>378664.333461</v>
+        <v>378664.074359</v>
       </c>
       <c r="G54" t="n">
-        <v>560702.768348</v>
+        <v>560701.9344199999</v>
       </c>
       <c r="H54" t="n">
-        <v>870764.6047</v>
+        <v>870761.834978</v>
       </c>
       <c r="I54" t="n">
-        <v>1464928.500922</v>
+        <v>1464916.222187</v>
       </c>
       <c r="J54" t="n">
         <v>3427952.732031</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>255115.531928</v>
+        <v>255115.595251</v>
       </c>
       <c r="F55" t="n">
-        <v>356508.955007</v>
+        <v>356509.214109</v>
       </c>
       <c r="G55" t="n">
-        <v>497918.216788</v>
+        <v>497919.050716</v>
       </c>
       <c r="H55" t="n">
-        <v>739291.903794</v>
+        <v>739294.673516</v>
       </c>
       <c r="I55" t="n">
-        <v>1201917.223926</v>
+        <v>1201929.502662</v>
       </c>
       <c r="J55" t="n">
         <v>202416.606069</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.465929</v>
+        <v>0.46199</v>
       </c>
       <c r="F58" t="n">
-        <v>1.304256</v>
+        <v>1.293228</v>
       </c>
       <c r="G58" t="n">
-        <v>3.350108</v>
+        <v>3.321783</v>
       </c>
       <c r="H58" t="n">
-        <v>8.580831999999999</v>
+        <v>8.508288</v>
       </c>
       <c r="I58" t="n">
-        <v>29.305294</v>
+        <v>29.057605</v>
       </c>
       <c r="J58" t="n">
         <v>88071.028009</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.06489499999999999</v>
+        <v>0.064346</v>
       </c>
       <c r="F59" t="n">
-        <v>0.189883</v>
+        <v>0.188277</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5069709999999999</v>
+        <v>0.502685</v>
       </c>
       <c r="H59" t="n">
-        <v>1.304091</v>
+        <v>1.293066</v>
       </c>
       <c r="I59" t="n">
-        <v>4.417714</v>
+        <v>4.380376</v>
       </c>
       <c r="J59" t="n">
         <v>13194.599062</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.206019</v>
+        <v>0.204277</v>
       </c>
       <c r="F60" t="n">
-        <v>0.435062</v>
+        <v>0.431384</v>
       </c>
       <c r="G60" t="n">
-        <v>0.841351</v>
+        <v>0.834237</v>
       </c>
       <c r="H60" t="n">
-        <v>1.755272</v>
+        <v>1.740433</v>
       </c>
       <c r="I60" t="n">
-        <v>5.265263</v>
+        <v>5.220761</v>
       </c>
       <c r="J60" t="n">
         <v>14684.585197</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>97215.251173</v>
+        <v>97215.25370099999</v>
       </c>
       <c r="F61" t="n">
-        <v>106087.733611</v>
+        <v>106087.740331</v>
       </c>
       <c r="G61" t="n">
-        <v>124999.48428</v>
+        <v>124999.49747</v>
       </c>
       <c r="H61" t="n">
-        <v>145187.504491</v>
+        <v>145187.528541</v>
       </c>
       <c r="I61" t="n">
-        <v>181111.374947</v>
+        <v>181111.428624</v>
       </c>
       <c r="J61" t="n">
         <v>211035.341686</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>55472.969172</v>
+        <v>55472.940895</v>
       </c>
       <c r="F62" t="n">
-        <v>64678.675979</v>
+        <v>64678.582782</v>
       </c>
       <c r="G62" t="n">
-        <v>79100.05353</v>
+        <v>79099.80533800001</v>
       </c>
       <c r="H62" t="n">
-        <v>92224.674887</v>
+        <v>92224.06045</v>
       </c>
       <c r="I62" t="n">
-        <v>112650.058976</v>
+        <v>112648.099657</v>
       </c>
       <c r="J62" t="n">
         <v>776936.296514</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>34161.785846</v>
+        <v>34161.765634</v>
       </c>
       <c r="F63" t="n">
-        <v>38691.672039</v>
+        <v>38691.611508</v>
       </c>
       <c r="G63" t="n">
-        <v>45677.486873</v>
+        <v>45677.341328</v>
       </c>
       <c r="H63" t="n">
-        <v>52940.647589</v>
+        <v>52940.304255</v>
       </c>
       <c r="I63" t="n">
-        <v>66366.318549</v>
+        <v>66365.21533599999</v>
       </c>
       <c r="J63" t="n">
         <v>466347.32529</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.032284</v>
+        <v>0.032011</v>
       </c>
       <c r="F64" t="n">
-        <v>0.080058</v>
+        <v>0.07938099999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>0.18221</v>
+        <v>0.18067</v>
       </c>
       <c r="H64" t="n">
-        <v>0.42092</v>
+        <v>0.417361</v>
       </c>
       <c r="I64" t="n">
-        <v>1.330977</v>
+        <v>1.319728</v>
       </c>
       <c r="J64" t="n">
         <v>3792.954481</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>295586.255898</v>
+        <v>295586.287014</v>
       </c>
       <c r="F65" t="n">
-        <v>350058.770214</v>
+        <v>350058.86214</v>
       </c>
       <c r="G65" t="n">
-        <v>455270.664413</v>
+        <v>455270.890849</v>
       </c>
       <c r="H65" t="n">
-        <v>584208.944163</v>
+        <v>584209.492198</v>
       </c>
       <c r="I65" t="n">
-        <v>801387.150393</v>
+        <v>801388.918913</v>
       </c>
       <c r="J65" t="n">
         <v>466911.997317</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>104398.199425</v>
+        <v>104398.212598</v>
       </c>
       <c r="F66" t="n">
-        <v>120643.159272</v>
+        <v>120643.19748</v>
       </c>
       <c r="G66" t="n">
-        <v>153241.603851</v>
+        <v>153241.69703</v>
       </c>
       <c r="H66" t="n">
-        <v>192110.359222</v>
+        <v>192110.582952</v>
       </c>
       <c r="I66" t="n">
-        <v>257649.353322</v>
+        <v>257650.071663</v>
       </c>
       <c r="J66" t="n">
         <v>92456.253971</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>123869.509277</v>
+        <v>123869.528251</v>
       </c>
       <c r="F67" t="n">
-        <v>146409.642672</v>
+        <v>146409.699106</v>
       </c>
       <c r="G67" t="n">
-        <v>194670.718465</v>
+        <v>194670.863769</v>
       </c>
       <c r="H67" t="n">
-        <v>255126.240224</v>
+        <v>255126.608493</v>
       </c>
       <c r="I67" t="n">
-        <v>355425.624959</v>
+        <v>355426.866468</v>
       </c>
       <c r="J67" t="n">
         <v>39400.556595</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>10354.322114</v>
+        <v>10354.318601</v>
       </c>
       <c r="F68" t="n">
-        <v>12436.652884</v>
+        <v>12436.640712</v>
       </c>
       <c r="G68" t="n">
-        <v>17039.546163</v>
+        <v>17039.506619</v>
       </c>
       <c r="H68" t="n">
-        <v>22193.600404</v>
+        <v>22193.482412</v>
       </c>
       <c r="I68" t="n">
-        <v>29506.679148</v>
+        <v>29506.247845</v>
       </c>
       <c r="J68" t="n">
         <v>191326.159496</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.071101</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>0.197465</v>
+        <v>0.195796</v>
       </c>
       <c r="G69" t="n">
-        <v>0.477251</v>
+        <v>0.473216</v>
       </c>
       <c r="H69" t="n">
-        <v>1.133211</v>
+        <v>1.12363</v>
       </c>
       <c r="I69" t="n">
-        <v>3.625602</v>
+        <v>3.594958</v>
       </c>
       <c r="J69" t="n">
         <v>10562.871012</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>78775.09905400001</v>
+        <v>78775.11061800001</v>
       </c>
       <c r="F70" t="n">
-        <v>87707.45890699999</v>
+        <v>87707.491308</v>
       </c>
       <c r="G70" t="n">
-        <v>107593.997743</v>
+        <v>107594.074643</v>
       </c>
       <c r="H70" t="n">
-        <v>129438.27243</v>
+        <v>129438.451188</v>
       </c>
       <c r="I70" t="n">
-        <v>166458.66556</v>
+        <v>166459.221294</v>
       </c>
       <c r="J70" t="n">
         <v>25825.681332</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>33551.288152</v>
+        <v>33551.282901</v>
       </c>
       <c r="F71" t="n">
-        <v>41031.982826</v>
+        <v>41031.964093</v>
       </c>
       <c r="G71" t="n">
-        <v>50753.116104</v>
+        <v>50753.066147</v>
       </c>
       <c r="H71" t="n">
-        <v>59706.730188</v>
+        <v>59706.608019</v>
       </c>
       <c r="I71" t="n">
-        <v>74285.160022</v>
+        <v>74284.76970800001</v>
       </c>
       <c r="J71" t="n">
         <v>223353.640833</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>70676.255575</v>
+        <v>70676.260631</v>
       </c>
       <c r="F72" t="n">
-        <v>72707.92509999999</v>
+        <v>72707.938167</v>
       </c>
       <c r="G72" t="n">
-        <v>83039.79842599999</v>
+        <v>83039.82597799999</v>
       </c>
       <c r="H72" t="n">
-        <v>94519.506843</v>
+        <v>94519.563584</v>
       </c>
       <c r="I72" t="n">
-        <v>116992.831774</v>
+        <v>116992.986919</v>
       </c>
       <c r="J72" t="n">
         <v>98473.088492</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>524.181973</v>
+        <v>524.164131</v>
       </c>
       <c r="F73" t="n">
-        <v>449.863901</v>
+        <v>449.829177</v>
       </c>
       <c r="G73" t="n">
-        <v>392.629918</v>
+        <v>392.577816</v>
       </c>
       <c r="H73" t="n">
-        <v>362.723314</v>
+        <v>362.637742</v>
       </c>
       <c r="I73" t="n">
-        <v>410.107442</v>
+        <v>409.884132</v>
       </c>
       <c r="J73" t="n">
         <v>70234.057249</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.025112</v>
+        <v>0.0249</v>
       </c>
       <c r="F74" t="n">
-        <v>0.087617</v>
+        <v>0.08687599999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>0.227166</v>
+        <v>0.225245</v>
       </c>
       <c r="H74" t="n">
-        <v>0.536234</v>
+        <v>0.531701</v>
       </c>
       <c r="I74" t="n">
-        <v>1.661408</v>
+        <v>1.647366</v>
       </c>
       <c r="J74" t="n">
         <v>4634.24919</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>12296.966476</v>
+        <v>12296.97517</v>
       </c>
       <c r="F75" t="n">
-        <v>15007.034244</v>
+        <v>15007.057031</v>
       </c>
       <c r="G75" t="n">
-        <v>22695.667841</v>
+        <v>22695.697159</v>
       </c>
       <c r="H75" t="n">
-        <v>35447.700637</v>
+        <v>35447.709374</v>
       </c>
       <c r="I75" t="n">
-        <v>55407.194493</v>
+        <v>55407.064903</v>
       </c>
       <c r="J75" t="n">
         <v>75913.850076</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>11141.592601</v>
+        <v>11141.494962</v>
       </c>
       <c r="F76" t="n">
-        <v>14005.071899</v>
+        <v>14004.640006</v>
       </c>
       <c r="G76" t="n">
-        <v>17275.437098</v>
+        <v>17274.281459</v>
       </c>
       <c r="H76" t="n">
-        <v>22887.008513</v>
+        <v>22883.972955</v>
       </c>
       <c r="I76" t="n">
-        <v>32872.507311</v>
+        <v>32861.886268</v>
       </c>
       <c r="J76" t="n">
         <v>408209.494743</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>48973.502316</v>
+        <v>48973.55713</v>
       </c>
       <c r="F77" t="n">
-        <v>67870.255626</v>
+        <v>67870.449592</v>
       </c>
       <c r="G77" t="n">
-        <v>107758.560773</v>
+        <v>107759.065094</v>
       </c>
       <c r="H77" t="n">
-        <v>163705.194736</v>
+        <v>163706.543046</v>
       </c>
       <c r="I77" t="n">
-        <v>237542.877913</v>
+        <v>237547.633777</v>
       </c>
       <c r="J77" t="n">
         <v>113858.181071</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>36686.906272</v>
+        <v>36686.805449</v>
       </c>
       <c r="F78" t="n">
-        <v>38893.48172</v>
+        <v>38893.152838</v>
       </c>
       <c r="G78" t="n">
-        <v>49898.3805</v>
+        <v>49897.394723</v>
       </c>
       <c r="H78" t="n">
-        <v>70511.695469</v>
+        <v>70508.735113</v>
       </c>
       <c r="I78" t="n">
-        <v>106274.744653</v>
+        <v>106263.393683</v>
       </c>
       <c r="J78" t="n">
         <v>539256.523918</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>41005.205241</v>
+        <v>41005.257191</v>
       </c>
       <c r="F79" t="n">
-        <v>65475.161178</v>
+        <v>65475.384922</v>
       </c>
       <c r="G79" t="n">
-        <v>129451.49749</v>
+        <v>129452.286579</v>
       </c>
       <c r="H79" t="n">
-        <v>248795.252349</v>
+        <v>248798.019648</v>
       </c>
       <c r="I79" t="n">
-        <v>448878.397449</v>
+        <v>448890.236592</v>
       </c>
       <c r="J79" t="n">
         <v>163211.106041</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6828.005498</v>
+        <v>6828.012822</v>
       </c>
       <c r="F80" t="n">
-        <v>7105.361181</v>
+        <v>7105.382223</v>
       </c>
       <c r="G80" t="n">
-        <v>9297.025046999999</v>
+        <v>9297.075338000001</v>
       </c>
       <c r="H80" t="n">
-        <v>13766.589353</v>
+        <v>13766.730302</v>
       </c>
       <c r="I80" t="n">
-        <v>21874.89597</v>
+        <v>21875.442459</v>
       </c>
       <c r="J80" t="n">
         <v>8559.217644</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>62597.111147</v>
+        <v>62597.192023</v>
       </c>
       <c r="F81" t="n">
-        <v>103783.694293</v>
+        <v>103784.059464</v>
       </c>
       <c r="G81" t="n">
-        <v>209889.497917</v>
+        <v>209890.844849</v>
       </c>
       <c r="H81" t="n">
-        <v>413832.697254</v>
+        <v>413837.659023</v>
       </c>
       <c r="I81" t="n">
-        <v>770502.291705</v>
+        <v>770524.554882</v>
       </c>
       <c r="J81" t="n">
         <v>206995.006957</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>391.666275</v>
+        <v>391.647944</v>
       </c>
       <c r="F82" t="n">
-        <v>481.780744</v>
+        <v>481.704904</v>
       </c>
       <c r="G82" t="n">
-        <v>710.566897</v>
+        <v>710.290985</v>
       </c>
       <c r="H82" t="n">
-        <v>1121.691641</v>
+        <v>1120.70503</v>
       </c>
       <c r="I82" t="n">
-        <v>1827.123522</v>
+        <v>1822.85282</v>
       </c>
       <c r="J82" t="n">
         <v>166657.81012</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>25307.977173</v>
+        <v>25307.99031</v>
       </c>
       <c r="F83" t="n">
-        <v>41390.859639</v>
+        <v>41390.869542</v>
       </c>
       <c r="G83" t="n">
-        <v>80780.500742</v>
+        <v>80780.19812</v>
       </c>
       <c r="H83" t="n">
-        <v>152198.113769</v>
+        <v>152195.869231</v>
       </c>
       <c r="I83" t="n">
-        <v>269043.636743</v>
+        <v>269030.604375</v>
       </c>
       <c r="J83" t="n">
         <v>915677.171217</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>85661.543186</v>
+        <v>85662.293853</v>
       </c>
       <c r="F86" t="n">
-        <v>105613.590982</v>
+        <v>105616.02196</v>
       </c>
       <c r="G86" t="n">
-        <v>121903.442693</v>
+        <v>121909.269385</v>
       </c>
       <c r="H86" t="n">
-        <v>151842.038774</v>
+        <v>151857.027381</v>
       </c>
       <c r="I86" t="n">
-        <v>201614.815409</v>
+        <v>201665.713135</v>
       </c>
       <c r="J86" t="n">
         <v>178234.350698</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6611.12692</v>
+        <v>6610.668205</v>
       </c>
       <c r="F87" t="n">
-        <v>9174.52657</v>
+        <v>9172.892405000001</v>
       </c>
       <c r="G87" t="n">
-        <v>12184.671492</v>
+        <v>12180.220068</v>
       </c>
       <c r="H87" t="n">
-        <v>17100.852453</v>
+        <v>17088.186679</v>
       </c>
       <c r="I87" t="n">
-        <v>25103.975667</v>
+        <v>25057.533355</v>
       </c>
       <c r="J87" t="n">
         <v>89091.455808</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>183058.248369</v>
+        <v>183057.923176</v>
       </c>
       <c r="F88" t="n">
-        <v>205668.257843</v>
+        <v>205667.887693</v>
       </c>
       <c r="G88" t="n">
-        <v>223874.93199</v>
+        <v>223875.033902</v>
       </c>
       <c r="H88" t="n">
-        <v>276685.045874</v>
+        <v>276686.672619</v>
       </c>
       <c r="I88" t="n">
-        <v>376586.47606</v>
+        <v>376594.337667</v>
       </c>
       <c r="J88" t="n">
         <v>452232.067106</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>39964.189461</v>
+        <v>39965.04822</v>
       </c>
       <c r="F89" t="n">
-        <v>47661.922455</v>
+        <v>47664.587445</v>
       </c>
       <c r="G89" t="n">
-        <v>55843.705584</v>
+        <v>55850.102828</v>
       </c>
       <c r="H89" t="n">
-        <v>71008.202823</v>
+        <v>71024.747757</v>
       </c>
       <c r="I89" t="n">
-        <v>96314.326661</v>
+        <v>96370.974025</v>
       </c>
       <c r="J89" t="n">
         <v>49550.111725</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>129239.906335</v>
+        <v>129239.991113</v>
       </c>
       <c r="F90" t="n">
-        <v>156002.937335</v>
+        <v>156003.376206</v>
       </c>
       <c r="G90" t="n">
-        <v>186588.820258</v>
+        <v>186589.961907</v>
       </c>
       <c r="H90" t="n">
-        <v>244172.052377</v>
+        <v>244175.068291</v>
       </c>
       <c r="I90" t="n">
-        <v>339694.822238</v>
+        <v>339705.125508</v>
       </c>
       <c r="J90" t="n">
         <v>403311.126695</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>60727.622185</v>
+        <v>60728.44296</v>
       </c>
       <c r="F91" t="n">
-        <v>74936.848111</v>
+        <v>74939.48760199999</v>
       </c>
       <c r="G91" t="n">
-        <v>87537.903758</v>
+        <v>87544.238169</v>
       </c>
       <c r="H91" t="n">
-        <v>108553.819036</v>
+        <v>108569.90972</v>
       </c>
       <c r="I91" t="n">
-        <v>141392.448063</v>
+        <v>141445.810979</v>
       </c>
       <c r="J91" t="n">
         <v>101878.778151</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>65781.820117</v>
+        <v>65783.45624</v>
       </c>
       <c r="F92" t="n">
-        <v>81863.048839</v>
+        <v>81868.302727</v>
       </c>
       <c r="G92" t="n">
-        <v>98712.90161299999</v>
+        <v>98725.819298</v>
       </c>
       <c r="H92" t="n">
-        <v>125807.914806</v>
+        <v>125841.325794</v>
       </c>
       <c r="I92" t="n">
-        <v>167658.255001</v>
+        <v>167770.617173</v>
       </c>
       <c r="J92" t="n">
         <v>68128.08340600001</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>904.707953</v>
+        <v>904.454846</v>
       </c>
       <c r="F93" t="n">
-        <v>1186.280936</v>
+        <v>1185.432812</v>
       </c>
       <c r="G93" t="n">
-        <v>1529.72292</v>
+        <v>1527.488276</v>
       </c>
       <c r="H93" t="n">
-        <v>2151.873845</v>
+        <v>2145.508032</v>
       </c>
       <c r="I93" t="n">
-        <v>3231.510185</v>
+        <v>3207.884544</v>
       </c>
       <c r="J93" t="n">
         <v>33395.710604</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>383966.353833</v>
+        <v>383959.820745</v>
       </c>
       <c r="F94" t="n">
-        <v>508847.262126</v>
+        <v>508824.949796</v>
       </c>
       <c r="G94" t="n">
-        <v>622256.9456719999</v>
+        <v>622201.283463</v>
       </c>
       <c r="H94" t="n">
-        <v>807734.2268459999</v>
+        <v>807588.7812420001</v>
       </c>
       <c r="I94" t="n">
-        <v>1102740.23401</v>
+        <v>1102245.823971</v>
       </c>
       <c r="J94" t="n">
         <v>1893511.918464</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>255643.224793</v>
+        <v>255646.308892</v>
       </c>
       <c r="F95" t="n">
-        <v>339331.726535</v>
+        <v>339342.18452</v>
       </c>
       <c r="G95" t="n">
-        <v>421448.544478</v>
+        <v>421474.757334</v>
       </c>
       <c r="H95" t="n">
-        <v>552391.130714</v>
+        <v>552460.493856</v>
       </c>
       <c r="I95" t="n">
-        <v>757864.722516</v>
+        <v>758104.0245159999</v>
       </c>
       <c r="J95" t="n">
         <v>627018.125417</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>92853.98790199999</v>
+        <v>92854.02312699999</v>
       </c>
       <c r="F96" t="n">
-        <v>109045.192662</v>
+        <v>109045.504226</v>
       </c>
       <c r="G96" t="n">
-        <v>119514.70748</v>
+        <v>119515.8244</v>
       </c>
       <c r="H96" t="n">
-        <v>146482.57113</v>
+        <v>146486.036007</v>
       </c>
       <c r="I96" t="n">
-        <v>196397.68602</v>
+        <v>196410.630612</v>
       </c>
       <c r="J96" t="n">
         <v>221342.180244</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>46713.738946</v>
+        <v>46714.038623</v>
       </c>
       <c r="F97" t="n">
-        <v>50778.795583</v>
+        <v>50779.762584</v>
       </c>
       <c r="G97" t="n">
-        <v>54066.550289</v>
+        <v>54068.849195</v>
       </c>
       <c r="H97" t="n">
-        <v>65954.4626</v>
+        <v>65960.433901</v>
       </c>
       <c r="I97" t="n">
-        <v>89236.135276</v>
+        <v>89256.931621</v>
       </c>
       <c r="J97" t="n">
         <v>84295.65889200001</v>
@@ -7822,19 +7822,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>426932.258207</v>
+        <v>426937.76391</v>
       </c>
       <c r="F98" t="n">
-        <v>432553.868245</v>
+        <v>432568.588882</v>
       </c>
       <c r="G98" t="n">
-        <v>504269.349156</v>
+        <v>504305.841519</v>
       </c>
       <c r="H98" t="n">
-        <v>557535.5728570001</v>
+        <v>557620.592216</v>
       </c>
       <c r="I98" t="n">
-        <v>738204.042249</v>
+        <v>738497.1562270001</v>
       </c>
       <c r="J98" t="n">
         <v>359480.063043</v>
@@ -7898,19 +7898,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>160740.192215</v>
+        <v>160738.02677</v>
       </c>
       <c r="F99" t="n">
-        <v>188509.182054</v>
+        <v>188502.540852</v>
       </c>
       <c r="G99" t="n">
-        <v>257422.421549</v>
+        <v>257403.472011</v>
       </c>
       <c r="H99" t="n">
-        <v>321165.613233</v>
+        <v>321116.85731</v>
       </c>
       <c r="I99" t="n">
-        <v>462695.295654</v>
+        <v>462516.594498</v>
       </c>
       <c r="J99" t="n">
         <v>914260.58423</v>
@@ -7974,19 +7974,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>207482.138414</v>
+        <v>207484.432359</v>
       </c>
       <c r="F100" t="n">
-        <v>208685.28755</v>
+        <v>208691.441207</v>
       </c>
       <c r="G100" t="n">
-        <v>246380.526178</v>
+        <v>246396.078625</v>
       </c>
       <c r="H100" t="n">
-        <v>276095.421628</v>
+        <v>276132.323106</v>
       </c>
       <c r="I100" t="n">
-        <v>369635.862569</v>
+        <v>369764.959693</v>
       </c>
       <c r="J100" t="n">
         <v>212493.624538</v>
@@ -8050,19 +8050,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>457395.585097</v>
+        <v>457403.859039</v>
       </c>
       <c r="F101" t="n">
-        <v>493067.356191</v>
+        <v>493090.486837</v>
       </c>
       <c r="G101" t="n">
-        <v>618927.421591</v>
+        <v>618987.9648590001</v>
       </c>
       <c r="H101" t="n">
-        <v>723389.160322</v>
+        <v>723536.0433519999</v>
       </c>
       <c r="I101" t="n">
-        <v>991870.461504</v>
+        <v>992389.527227</v>
       </c>
       <c r="J101" t="n">
         <v>270301.076996</v>
@@ -8126,19 +8126,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>999139.5333069999</v>
+        <v>999133.777974</v>
       </c>
       <c r="F102" t="n">
-        <v>1139212.331639</v>
+        <v>1139195.64489</v>
       </c>
       <c r="G102" t="n">
-        <v>1528809.873746</v>
+        <v>1528764.05399</v>
       </c>
       <c r="H102" t="n">
-        <v>1900563.966438</v>
+        <v>1900447.985744</v>
       </c>
       <c r="I102" t="n">
-        <v>2752326.712554</v>
+        <v>2751902.583267</v>
       </c>
       <c r="J102" t="n">
         <v>4293497.609719</v>
@@ -8202,19 +8202,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1701888.552094</v>
+        <v>1701892.556155</v>
       </c>
       <c r="F103" t="n">
-        <v>1661854.032004</v>
+        <v>1661866.887913</v>
       </c>
       <c r="G103" t="n">
-        <v>1884149.354964</v>
+        <v>1884186.496</v>
       </c>
       <c r="H103" t="n">
-        <v>2040066.590245</v>
+        <v>2040161.752323</v>
       </c>
       <c r="I103" t="n">
-        <v>2662261.899692</v>
+        <v>2662609.150208</v>
       </c>
       <c r="J103" t="n">
         <v>2508538.774623</v>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>123646.422197</v>
+        <v>123644.732933</v>
       </c>
       <c r="F104" t="n">
-        <v>135502.412309</v>
+        <v>135497.701085</v>
       </c>
       <c r="G104" t="n">
-        <v>173453.556793</v>
+        <v>173441.28029</v>
       </c>
       <c r="H104" t="n">
-        <v>209286.136518</v>
+        <v>209255.850037</v>
       </c>
       <c r="I104" t="n">
-        <v>297540.080555</v>
+        <v>297430.292585</v>
       </c>
       <c r="J104" t="n">
         <v>577756.371792</v>
@@ -8354,19 +8354,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>48829.595894</v>
+        <v>48828.407669</v>
       </c>
       <c r="F105" t="n">
-        <v>54385.158167</v>
+        <v>54381.832681</v>
       </c>
       <c r="G105" t="n">
-        <v>71591.341877</v>
+        <v>71582.462161</v>
       </c>
       <c r="H105" t="n">
-        <v>87284.897952</v>
+        <v>87263.014429</v>
       </c>
       <c r="I105" t="n">
-        <v>124290.755519</v>
+        <v>124212.550312</v>
       </c>
       <c r="J105" t="n">
         <v>298334.551343</v>
@@ -8430,19 +8430,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1145570.11229</v>
+        <v>1145572.734782</v>
       </c>
       <c r="F106" t="n">
-        <v>1316482.858931</v>
+        <v>1316490.344691</v>
       </c>
       <c r="G106" t="n">
-        <v>1795989.792488</v>
+        <v>1796009.687906</v>
       </c>
       <c r="H106" t="n">
-        <v>2249280.254836</v>
+        <v>2249329.681083</v>
       </c>
       <c r="I106" t="n">
-        <v>3254182.522644</v>
+        <v>3254362.648304</v>
       </c>
       <c r="J106" t="n">
         <v>3780960.848038</v>
@@ -8506,19 +8506,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>9019.465956</v>
+        <v>9018.725587000001</v>
       </c>
       <c r="F107" t="n">
-        <v>10923.468358</v>
+        <v>10921.150807</v>
       </c>
       <c r="G107" t="n">
-        <v>14602.49327</v>
+        <v>14596.172808</v>
       </c>
       <c r="H107" t="n">
-        <v>17961.505881</v>
+        <v>17945.750948</v>
       </c>
       <c r="I107" t="n">
-        <v>26035.050432</v>
+        <v>25977.60093</v>
       </c>
       <c r="J107" t="n">
         <v>141446.587333</v>
@@ -8582,19 +8582,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>156699.611167</v>
+        <v>156692.470185</v>
       </c>
       <c r="F108" t="n">
-        <v>171315.277978</v>
+        <v>171295.433621</v>
       </c>
       <c r="G108" t="n">
-        <v>214951.764399</v>
+        <v>214901.342601</v>
       </c>
       <c r="H108" t="n">
-        <v>251168.246857</v>
+        <v>251049.310597</v>
       </c>
       <c r="I108" t="n">
-        <v>345752.044427</v>
+        <v>345340.934471</v>
       </c>
       <c r="J108" t="n">
         <v>1155560.072506</v>
@@ -8658,19 +8658,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>216541.111453</v>
+        <v>216543.40612</v>
       </c>
       <c r="F109" t="n">
-        <v>237375.233504</v>
+        <v>237381.790488</v>
       </c>
       <c r="G109" t="n">
-        <v>318039.47209</v>
+        <v>318057.681332</v>
       </c>
       <c r="H109" t="n">
-        <v>406770.032749</v>
+        <v>406817.740509</v>
       </c>
       <c r="I109" t="n">
-        <v>614603.327377</v>
+        <v>614786.054867</v>
       </c>
       <c r="J109" t="n">
         <v>459639.487823</v>
@@ -8734,19 +8734,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>830390.016391</v>
+        <v>830404.393245</v>
       </c>
       <c r="F110" t="n">
-        <v>966855.7370880001</v>
+        <v>966898.974859</v>
       </c>
       <c r="G110" t="n">
-        <v>1320707.042206</v>
+        <v>1320829.658763</v>
       </c>
       <c r="H110" t="n">
-        <v>1649438.345079</v>
+        <v>1649755.256095</v>
       </c>
       <c r="I110" t="n">
-        <v>2372240.71841</v>
+        <v>2373413.479797</v>
       </c>
       <c r="J110" t="n">
         <v>800079.819623</v>
@@ -8810,19 +8810,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>723991.330848</v>
+        <v>723988.97511</v>
       </c>
       <c r="F111" t="n">
-        <v>816580.486411</v>
+        <v>816573.833791</v>
       </c>
       <c r="G111" t="n">
-        <v>1065695.927695</v>
+        <v>1065678.936405</v>
       </c>
       <c r="H111" t="n">
-        <v>1287280.078587</v>
+        <v>1287240.374253</v>
       </c>
       <c r="I111" t="n">
-        <v>1825872.592741</v>
+        <v>1825736.309945</v>
       </c>
       <c r="J111" t="n">
         <v>2535945.202885</v>
@@ -8886,19 +8886,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>597014.57447</v>
+        <v>596996.2381599999</v>
       </c>
       <c r="F112" t="n">
-        <v>683440.919861</v>
+        <v>683386.957685</v>
       </c>
       <c r="G112" t="n">
-        <v>922970.229577</v>
+        <v>922819.438309</v>
       </c>
       <c r="H112" t="n">
-        <v>1150463.775528</v>
+        <v>1150077.066706</v>
       </c>
       <c r="I112" t="n">
-        <v>1667495.035773</v>
+        <v>1666066.559768</v>
       </c>
       <c r="J112" t="n">
         <v>4794900.587887</v>
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>57866.915724</v>
+        <v>57866.705241</v>
       </c>
       <c r="F113" t="n">
-        <v>51552.774015</v>
+        <v>51552.279089</v>
       </c>
       <c r="G113" t="n">
-        <v>61466.278691</v>
+        <v>61465.232025</v>
       </c>
       <c r="H113" t="n">
-        <v>87413.841637</v>
+        <v>87411.360245</v>
       </c>
       <c r="I113" t="n">
-        <v>119578.920517</v>
+        <v>119571.915472</v>
       </c>
       <c r="J113" t="n">
         <v>164600.309187</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>28462.2409</v>
+        <v>28462.640299</v>
       </c>
       <c r="F114" t="n">
-        <v>35814.875252</v>
+        <v>35816.216506</v>
       </c>
       <c r="G114" t="n">
-        <v>63688.942873</v>
+        <v>63693.914144</v>
       </c>
       <c r="H114" t="n">
-        <v>118376.618925</v>
+        <v>118395.616342</v>
       </c>
       <c r="I114" t="n">
-        <v>185327.917635</v>
+        <v>185403.838835</v>
       </c>
       <c r="J114" t="n">
         <v>44125.147046</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>114008.009376</v>
+        <v>114007.82046</v>
       </c>
       <c r="F115" t="n">
-        <v>116762.378483</v>
+        <v>116761.532154</v>
       </c>
       <c r="G115" t="n">
-        <v>174223.110494</v>
+        <v>174219.185888</v>
       </c>
       <c r="H115" t="n">
-        <v>293151.295423</v>
+        <v>293134.779398</v>
       </c>
       <c r="I115" t="n">
-        <v>444533.386669</v>
+        <v>444464.470514</v>
       </c>
       <c r="J115" t="n">
         <v>770178.075601</v>
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>25217.114169</v>
+        <v>25217.127222</v>
       </c>
       <c r="F116" t="n">
-        <v>25465.085668</v>
+        <v>25465.120421</v>
       </c>
       <c r="G116" t="n">
-        <v>31947.649581</v>
+        <v>31947.741481</v>
       </c>
       <c r="H116" t="n">
-        <v>43582.297073</v>
+        <v>43582.558561</v>
       </c>
       <c r="I116" t="n">
-        <v>64504.867456</v>
+        <v>64505.867752</v>
       </c>
       <c r="J116" t="n">
         <v>16741.622693</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>34800.238195</v>
+        <v>34800.244901</v>
       </c>
       <c r="F117" t="n">
-        <v>43403.088729</v>
+        <v>43403.10451</v>
       </c>
       <c r="G117" t="n">
-        <v>60045.031448</v>
+        <v>60045.068294</v>
       </c>
       <c r="H117" t="n">
-        <v>86104.86511300001</v>
+        <v>86104.960515</v>
       </c>
       <c r="I117" t="n">
-        <v>130337.567058</v>
+        <v>130337.908678</v>
       </c>
       <c r="J117" t="n">
         <v>145751.622491</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>65563.92292500001</v>
+        <v>65563.921969</v>
       </c>
       <c r="F118" t="n">
-        <v>64674.480485</v>
+        <v>64674.478406</v>
       </c>
       <c r="G118" t="n">
-        <v>78777.570635</v>
+        <v>78777.568766</v>
       </c>
       <c r="H118" t="n">
-        <v>104879.065938</v>
+        <v>104879.070139</v>
       </c>
       <c r="I118" t="n">
-        <v>152499.59318</v>
+        <v>152499.63521</v>
       </c>
       <c r="J118" t="n">
         <v>187657.331013</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>13864.290939</v>
+        <v>13864.291731</v>
       </c>
       <c r="F119" t="n">
-        <v>16510.181346</v>
+        <v>16510.181716</v>
       </c>
       <c r="G119" t="n">
-        <v>23910.938559</v>
+        <v>23910.934234</v>
       </c>
       <c r="H119" t="n">
-        <v>36398.792781</v>
+        <v>36398.766589</v>
       </c>
       <c r="I119" t="n">
-        <v>58236.046494</v>
+        <v>58235.905471</v>
       </c>
       <c r="J119" t="n">
         <v>89433.052914</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>9960.253255</v>
+        <v>9960.256642</v>
       </c>
       <c r="F120" t="n">
-        <v>10124.722816</v>
+        <v>10124.731899</v>
       </c>
       <c r="G120" t="n">
-        <v>12813.55147</v>
+        <v>12813.575768</v>
       </c>
       <c r="H120" t="n">
-        <v>17675.169501</v>
+        <v>17675.239638</v>
       </c>
       <c r="I120" t="n">
-        <v>26502.77732</v>
+        <v>26503.049802</v>
       </c>
       <c r="J120" t="n">
         <v>16141.694715</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>64609.364633</v>
+        <v>64609.36176</v>
       </c>
       <c r="F121" t="n">
-        <v>75851.843217</v>
+        <v>75851.822527</v>
       </c>
       <c r="G121" t="n">
-        <v>108049.045572</v>
+        <v>108048.95456</v>
       </c>
       <c r="H121" t="n">
-        <v>160281.077168</v>
+        <v>160280.739996</v>
       </c>
       <c r="I121" t="n">
-        <v>248534.989178</v>
+        <v>248533.52822</v>
       </c>
       <c r="J121" t="n">
         <v>424128.559781</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>523759.105884</v>
+        <v>523759.085775</v>
       </c>
       <c r="F122" t="n">
-        <v>534377.633999</v>
+        <v>534377.596781</v>
       </c>
       <c r="G122" t="n">
-        <v>680741.133674</v>
+        <v>680741.077835</v>
       </c>
       <c r="H122" t="n">
-        <v>949167.579054</v>
+        <v>949167.511189</v>
       </c>
       <c r="I122" t="n">
-        <v>1444686.146198</v>
+        <v>1444686.091751</v>
       </c>
       <c r="J122" t="n">
         <v>1895662.105869</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>186062.459521</v>
+        <v>186073.335896</v>
       </c>
       <c r="F123" t="n">
-        <v>203097.796792</v>
+        <v>203126.478874</v>
       </c>
       <c r="G123" t="n">
-        <v>238027.028551</v>
+        <v>238091.532968</v>
       </c>
       <c r="H123" t="n">
-        <v>275581.207648</v>
+        <v>275725.782869</v>
       </c>
       <c r="I123" t="n">
-        <v>375855.608781</v>
+        <v>376335.33687</v>
       </c>
       <c r="J123" t="n">
         <v>53817.186423</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>500265.79264</v>
+        <v>500273.052112</v>
       </c>
       <c r="F124" t="n">
-        <v>548215.457156</v>
+        <v>548233.313602</v>
       </c>
       <c r="G124" t="n">
-        <v>635715.683475</v>
+        <v>635751.471701</v>
       </c>
       <c r="H124" t="n">
-        <v>731850.739471</v>
+        <v>731923.836504</v>
       </c>
       <c r="I124" t="n">
-        <v>992306.8745189999</v>
+        <v>992531.778916</v>
       </c>
       <c r="J124" t="n">
         <v>1027058.424442</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>196935.053839</v>
+        <v>196916.917992</v>
       </c>
       <c r="F125" t="n">
-        <v>199852.495774</v>
+        <v>199805.957246</v>
       </c>
       <c r="G125" t="n">
-        <v>212358.791392</v>
+        <v>212258.498749</v>
       </c>
       <c r="H125" t="n">
-        <v>229504.456503</v>
+        <v>229286.784248</v>
       </c>
       <c r="I125" t="n">
-        <v>301025.1913</v>
+        <v>300320.558813</v>
       </c>
       <c r="J125" t="n">
         <v>947177.794963</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4885.16076</v>
+        <v>4885.159918</v>
       </c>
       <c r="F130" t="n">
-        <v>28539.356564</v>
+        <v>28539.339261</v>
       </c>
       <c r="G130" t="n">
-        <v>62330.689358</v>
+        <v>62330.57665</v>
       </c>
       <c r="H130" t="n">
-        <v>134057.587873</v>
+        <v>134056.74213</v>
       </c>
       <c r="I130" t="n">
-        <v>300378.212741</v>
+        <v>300366.151716</v>
       </c>
       <c r="J130" t="n">
         <v>11889475.030984</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2.2e-05</v>
+        <v>5e-06</v>
       </c>
       <c r="F131" t="n">
-        <v>0.000671</v>
+        <v>0.000146</v>
       </c>
       <c r="G131" t="n">
-        <v>0.004632</v>
+        <v>0.001009</v>
       </c>
       <c r="H131" t="n">
-        <v>0.033803</v>
+        <v>0.007361</v>
       </c>
       <c r="I131" t="n">
-        <v>0.459816</v>
+        <v>0.100138</v>
       </c>
       <c r="J131" t="n">
         <v>328885.398401</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>80794.610818</v>
+        <v>80794.611492</v>
       </c>
       <c r="F132" t="n">
-        <v>433634.273001</v>
+        <v>433634.284645</v>
       </c>
       <c r="G132" t="n">
-        <v>848028.61571</v>
+        <v>848028.678611</v>
       </c>
       <c r="H132" t="n">
-        <v>1630278.161919</v>
+        <v>1630278.568382</v>
       </c>
       <c r="I132" t="n">
-        <v>3311138.85675</v>
+        <v>3311144.063595</v>
       </c>
       <c r="J132" t="n">
         <v>266311.223673</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>12208.8861</v>
+        <v>12208.886207</v>
       </c>
       <c r="F133" t="n">
-        <v>93368.387776</v>
+        <v>93368.390358</v>
       </c>
       <c r="G133" t="n">
-        <v>253840.760613</v>
+        <v>253840.779368</v>
       </c>
       <c r="H133" t="n">
-        <v>623836.555239</v>
+        <v>623836.705917</v>
       </c>
       <c r="I133" t="n">
-        <v>1503592.052191</v>
+        <v>1503594.312677</v>
       </c>
       <c r="J133" t="n">
         <v>241877.748426</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>23317.158793</v>
+        <v>23317.158941</v>
       </c>
       <c r="F134" t="n">
-        <v>118392.430695</v>
+        <v>118392.43331</v>
       </c>
       <c r="G134" t="n">
-        <v>229106.738313</v>
+        <v>229106.752959</v>
       </c>
       <c r="H134" t="n">
-        <v>451563.853721</v>
+        <v>451563.953382</v>
       </c>
       <c r="I134" t="n">
-        <v>957961.833459</v>
+        <v>957963.186906</v>
       </c>
       <c r="J134" t="n">
         <v>212018.628156</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>8072.128459</v>
+        <v>8072.12853</v>
       </c>
       <c r="F135" t="n">
-        <v>55627.831587</v>
+        <v>55627.833184</v>
       </c>
       <c r="G135" t="n">
-        <v>140809.751822</v>
+        <v>140809.762925</v>
       </c>
       <c r="H135" t="n">
-        <v>333198.139026</v>
+        <v>333198.226612</v>
       </c>
       <c r="I135" t="n">
-        <v>796009.558357</v>
+        <v>796010.868661</v>
       </c>
       <c r="J135" t="n">
         <v>20326.493901</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1325.395419</v>
+        <v>1325.395268</v>
       </c>
       <c r="F136" t="n">
-        <v>6738.439729</v>
+        <v>6738.437799</v>
       </c>
       <c r="G136" t="n">
-        <v>12151.860246</v>
+        <v>12151.853997</v>
       </c>
       <c r="H136" t="n">
-        <v>21642.843539</v>
+        <v>21642.821097</v>
       </c>
       <c r="I136" t="n">
-        <v>42133.600845</v>
+        <v>42133.426146</v>
       </c>
       <c r="J136" t="n">
         <v>190518.388852</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>10012.485123</v>
+        <v>10012.485206</v>
       </c>
       <c r="F137" t="n">
-        <v>55749.9628</v>
+        <v>55749.964268</v>
       </c>
       <c r="G137" t="n">
-        <v>108823.018738</v>
+        <v>108823.026645</v>
       </c>
       <c r="H137" t="n">
-        <v>207895.883553</v>
+        <v>207895.934422</v>
       </c>
       <c r="I137" t="n">
-        <v>425462.106789</v>
+        <v>425462.762688</v>
       </c>
       <c r="J137" t="n">
         <v>48425.264539</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>116.757784</v>
+        <v>116.75777</v>
       </c>
       <c r="F138" t="n">
-        <v>631.976522</v>
+        <v>631.976276</v>
       </c>
       <c r="G138" t="n">
-        <v>1243.395884</v>
+        <v>1243.394689</v>
       </c>
       <c r="H138" t="n">
-        <v>2373.340167</v>
+        <v>2373.333932</v>
       </c>
       <c r="I138" t="n">
-        <v>4730.681359</v>
+        <v>4730.619935</v>
       </c>
       <c r="J138" t="n">
         <v>49241.743831</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>373.763602</v>
+        <v>373.763604</v>
       </c>
       <c r="F139" t="n">
-        <v>2138.07429</v>
+        <v>2138.074326</v>
       </c>
       <c r="G139" t="n">
-        <v>4612.727743</v>
+        <v>4612.727948</v>
       </c>
       <c r="H139" t="n">
-        <v>9854.014017</v>
+        <v>9854.015428999999</v>
       </c>
       <c r="I139" t="n">
-        <v>21984.347496</v>
+        <v>21984.367005</v>
       </c>
       <c r="J139" t="n">
         <v>16214.170207</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>518.804212</v>
+        <v>518.804081</v>
       </c>
       <c r="F140" t="n">
-        <v>2707.54433</v>
+        <v>2707.542528</v>
       </c>
       <c r="G140" t="n">
-        <v>5413.591683</v>
+        <v>5413.583377</v>
       </c>
       <c r="H140" t="n">
-        <v>11135.696761</v>
+        <v>11135.646564</v>
       </c>
       <c r="I140" t="n">
-        <v>24912.016894</v>
+        <v>24911.350889</v>
       </c>
       <c r="J140" t="n">
         <v>697537.151094</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1965.078388</v>
+        <v>1965.078405</v>
       </c>
       <c r="F141" t="n">
-        <v>11534.098582</v>
+        <v>11534.098904</v>
       </c>
       <c r="G141" t="n">
-        <v>25324.408862</v>
+        <v>25324.410806</v>
       </c>
       <c r="H141" t="n">
-        <v>54528.067401</v>
+        <v>54528.081373</v>
       </c>
       <c r="I141" t="n">
-        <v>122452.324052</v>
+        <v>122452.520804</v>
       </c>
       <c r="J141" t="n">
         <v>7367.865011</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5828.241721</v>
+        <v>5828.241773</v>
       </c>
       <c r="F142" t="n">
-        <v>54042.905004</v>
+        <v>54042.906546</v>
       </c>
       <c r="G142" t="n">
-        <v>191470.330432</v>
+        <v>191470.345053</v>
       </c>
       <c r="H142" t="n">
-        <v>576434.421847</v>
+        <v>576434.562265</v>
       </c>
       <c r="I142" t="n">
-        <v>1585113.0362</v>
+        <v>1585115.355788</v>
       </c>
       <c r="J142" t="n">
         <v>403138.480873</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>7288.968998</v>
+        <v>7288.97401</v>
       </c>
       <c r="F146" t="n">
-        <v>7360.0271</v>
+        <v>7360.041762</v>
       </c>
       <c r="G146" t="n">
-        <v>7766.538735</v>
+        <v>7766.574124</v>
       </c>
       <c r="H146" t="n">
-        <v>9051.997171999999</v>
+        <v>9052.086968</v>
       </c>
       <c r="I146" t="n">
-        <v>12506.497248</v>
+        <v>12506.821668</v>
       </c>
       <c r="J146" t="n">
         <v>4107.165224</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3036.484168</v>
+        <v>3036.479259</v>
       </c>
       <c r="F147" t="n">
-        <v>3547.184908</v>
+        <v>3547.168963</v>
       </c>
       <c r="G147" t="n">
-        <v>4227.48509</v>
+        <v>4227.444577</v>
       </c>
       <c r="H147" t="n">
-        <v>5210.008324</v>
+        <v>5209.904618</v>
       </c>
       <c r="I147" t="n">
-        <v>7288.407821</v>
+        <v>7288.033472</v>
       </c>
       <c r="J147" t="n">
         <v>25332.597337</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>303583.873778</v>
+        <v>303583.873674</v>
       </c>
       <c r="F148" t="n">
-        <v>366411.528364</v>
+        <v>366411.529647</v>
       </c>
       <c r="G148" t="n">
-        <v>464043.94662</v>
+        <v>464043.951745</v>
       </c>
       <c r="H148" t="n">
-        <v>602536.980523</v>
+        <v>602536.994433</v>
       </c>
       <c r="I148" t="n">
-        <v>868179.706082</v>
+        <v>868179.75601</v>
       </c>
       <c r="J148" t="n">
         <v>1206905.642883</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>48871.384363</v>
+        <v>48870.988428</v>
       </c>
       <c r="F149" t="n">
-        <v>58124.641661</v>
+        <v>58123.533146</v>
       </c>
       <c r="G149" t="n">
-        <v>72334.480751</v>
+        <v>72331.712161</v>
       </c>
       <c r="H149" t="n">
-        <v>96685.552817</v>
+        <v>96677.71846400001</v>
       </c>
       <c r="I149" t="n">
-        <v>140413.227266</v>
+        <v>140382.543668</v>
       </c>
       <c r="J149" t="n">
         <v>259327.240081</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>395463.004797</v>
+        <v>395463.297119</v>
       </c>
       <c r="F150" t="n">
-        <v>464339.381444</v>
+        <v>464340.718024</v>
       </c>
       <c r="G150" t="n">
-        <v>565134.4360409999</v>
+        <v>565137.4283030001</v>
       </c>
       <c r="H150" t="n">
-        <v>710984.519552</v>
+        <v>710989.013917</v>
       </c>
       <c r="I150" t="n">
-        <v>957757.476247</v>
+        <v>957758.1850910001</v>
       </c>
       <c r="J150" t="n">
         <v>1217266.852509</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>68672.384808</v>
+        <v>68669.828477</v>
       </c>
       <c r="F151" t="n">
-        <v>83933.37319899999</v>
+        <v>83925.586977</v>
       </c>
       <c r="G151" t="n">
-        <v>106548.67281</v>
+        <v>106528.73216</v>
       </c>
       <c r="H151" t="n">
-        <v>139552.077552</v>
+        <v>139499.079175</v>
       </c>
       <c r="I151" t="n">
-        <v>192245.537114</v>
+        <v>192061.239091</v>
       </c>
       <c r="J151" t="n">
         <v>607919.516597</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>232295.653111</v>
+        <v>232290.41468</v>
       </c>
       <c r="F152" t="n">
-        <v>297429.32621</v>
+        <v>297412.475999</v>
       </c>
       <c r="G152" t="n">
-        <v>370674.876539</v>
+        <v>370632.331403</v>
       </c>
       <c r="H152" t="n">
-        <v>464388.411527</v>
+        <v>464279.73862</v>
       </c>
       <c r="I152" t="n">
-        <v>608570.4171880001</v>
+        <v>608208.418892</v>
       </c>
       <c r="J152" t="n">
         <v>1429343.547943</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>294579.394527</v>
+        <v>294586.089782</v>
       </c>
       <c r="F153" t="n">
-        <v>352351.27125</v>
+        <v>352371.776116</v>
       </c>
       <c r="G153" t="n">
-        <v>452525.756559</v>
+        <v>452578.418425</v>
       </c>
       <c r="H153" t="n">
-        <v>619947.6350379999</v>
+        <v>620089.58131</v>
       </c>
       <c r="I153" t="n">
-        <v>906164.946495</v>
+        <v>906670.654395</v>
       </c>
       <c r="J153" t="n">
         <v>171962.367918</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>119986.934395</v>
+        <v>119988.137515</v>
       </c>
       <c r="F154" t="n">
-        <v>150982.435588</v>
+        <v>150986.339091</v>
       </c>
       <c r="G154" t="n">
-        <v>188148.37597</v>
+        <v>188157.976218</v>
       </c>
       <c r="H154" t="n">
-        <v>236316.506264</v>
+        <v>236339.571266</v>
       </c>
       <c r="I154" t="n">
-        <v>307716.04833</v>
+        <v>307786.611503</v>
       </c>
       <c r="J154" t="n">
         <v>240315.169772</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>190534.882382</v>
+        <v>190522.49418</v>
       </c>
       <c r="F155" t="n">
-        <v>194362.754562</v>
+        <v>194332.38497</v>
       </c>
       <c r="G155" t="n">
-        <v>241146.023991</v>
+        <v>241075.504544</v>
       </c>
       <c r="H155" t="n">
-        <v>311886.915528</v>
+        <v>311718.967916</v>
       </c>
       <c r="I155" t="n">
-        <v>408131.136319</v>
+        <v>407630.156013</v>
       </c>
       <c r="J155" t="n">
         <v>292200.834949</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>372498.325975</v>
+        <v>372540.510565</v>
       </c>
       <c r="F156" t="n">
-        <v>354584.742732</v>
+        <v>354687.173196</v>
       </c>
       <c r="G156" t="n">
-        <v>404615.116726</v>
+        <v>404856.174254</v>
       </c>
       <c r="H156" t="n">
-        <v>474160.788864</v>
+        <v>474743.741963</v>
       </c>
       <c r="I156" t="n">
-        <v>563236.420651</v>
+        <v>564998.574969</v>
       </c>
       <c r="J156" t="n">
         <v>1441306.963995</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4192.947133</v>
+        <v>4194.157411</v>
       </c>
       <c r="F157" t="n">
-        <v>5037.143968</v>
+        <v>5040.804324</v>
       </c>
       <c r="G157" t="n">
-        <v>7016.403553</v>
+        <v>7026.703164</v>
       </c>
       <c r="H157" t="n">
-        <v>9240.622708999999</v>
+        <v>9267.949635000001</v>
       </c>
       <c r="I157" t="n">
-        <v>11578.682659</v>
+        <v>11663.450112</v>
       </c>
       <c r="J157" t="n">
         <v>51065.749695</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>206994.565834</v>
+        <v>207002.163333</v>
       </c>
       <c r="F158" t="n">
-        <v>174466.754367</v>
+        <v>174483.805971</v>
       </c>
       <c r="G158" t="n">
-        <v>174925.363825</v>
+        <v>174962.876117</v>
       </c>
       <c r="H158" t="n">
-        <v>186572.279694</v>
+        <v>186660.208072</v>
       </c>
       <c r="I158" t="n">
-        <v>208615.843337</v>
+        <v>208880.471136</v>
       </c>
       <c r="J158" t="n">
         <v>351268.213236</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1786.63461</v>
+        <v>1787.02979</v>
       </c>
       <c r="F159" t="n">
-        <v>1636.76631</v>
+        <v>1637.679512</v>
       </c>
       <c r="G159" t="n">
-        <v>1830.106918</v>
+        <v>1832.177404</v>
       </c>
       <c r="H159" t="n">
-        <v>2113.724854</v>
+        <v>2118.566845</v>
       </c>
       <c r="I159" t="n">
-        <v>2507.6011</v>
+        <v>2521.921244</v>
       </c>
       <c r="J159" t="n">
         <v>9231.515389</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>435366.832067</v>
+        <v>435327.832721</v>
       </c>
       <c r="F160" t="n">
-        <v>430490.547298</v>
+        <v>430396.861265</v>
       </c>
       <c r="G160" t="n">
-        <v>531058.952334</v>
+        <v>530838.531864</v>
       </c>
       <c r="H160" t="n">
-        <v>683181.82609</v>
+        <v>682646.72331</v>
       </c>
       <c r="I160" t="n">
-        <v>885063.650561</v>
+        <v>883438.7611530001</v>
       </c>
       <c r="J160" t="n">
         <v>361973.188215</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>7.964293</v>
+        <v>7.959586</v>
       </c>
       <c r="F162" t="n">
-        <v>6.834976</v>
+        <v>6.827573</v>
       </c>
       <c r="G162" t="n">
-        <v>7.762505</v>
+        <v>7.750409</v>
       </c>
       <c r="H162" t="n">
-        <v>11.250855</v>
+        <v>11.227082</v>
       </c>
       <c r="I162" t="n">
-        <v>25.022324</v>
+        <v>24.952116</v>
       </c>
       <c r="J162" t="n">
         <v>27325.019829</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4136.82962</v>
+        <v>4136.829592</v>
       </c>
       <c r="F163" t="n">
-        <v>4856.840816</v>
+        <v>4856.84058</v>
       </c>
       <c r="G163" t="n">
-        <v>7230.924809</v>
+        <v>7230.92356</v>
       </c>
       <c r="H163" t="n">
-        <v>10482.283061</v>
+        <v>10482.278284</v>
       </c>
       <c r="I163" t="n">
-        <v>15108.03572</v>
+        <v>15108.015843</v>
       </c>
       <c r="J163" t="n">
         <v>28164.951212</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>129354.254377</v>
+        <v>129354.266074</v>
       </c>
       <c r="F164" t="n">
-        <v>165930.603553</v>
+        <v>165930.640503</v>
       </c>
       <c r="G164" t="n">
-        <v>262637.182074</v>
+        <v>262637.296768</v>
       </c>
       <c r="H164" t="n">
-        <v>407856.116721</v>
+        <v>407856.467424</v>
       </c>
       <c r="I164" t="n">
-        <v>631693.761257</v>
+        <v>631695.105583</v>
       </c>
       <c r="J164" t="n">
         <v>273568.705262</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>109789.110869</v>
+        <v>109789.121039</v>
       </c>
       <c r="F165" t="n">
-        <v>125361.209615</v>
+        <v>125361.238868</v>
       </c>
       <c r="G165" t="n">
-        <v>159795.113943</v>
+        <v>159795.190054</v>
       </c>
       <c r="H165" t="n">
-        <v>210492.519051</v>
+        <v>210492.723688</v>
       </c>
       <c r="I165" t="n">
-        <v>294123.680163</v>
+        <v>294124.407783</v>
       </c>
       <c r="J165" t="n">
         <v>72400.77632400001</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>468834.390527</v>
+        <v>468834.438684</v>
       </c>
       <c r="F166" t="n">
-        <v>498986.122028</v>
+        <v>498986.252113</v>
       </c>
       <c r="G166" t="n">
-        <v>652667.214842</v>
+        <v>652667.560298</v>
       </c>
       <c r="H166" t="n">
-        <v>873755.912696</v>
+        <v>873756.851152</v>
       </c>
       <c r="I166" t="n">
-        <v>1207628.197577</v>
+        <v>1207631.485842</v>
       </c>
       <c r="J166" t="n">
         <v>167203.503912</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>75481.70262500001</v>
+        <v>75481.647518</v>
       </c>
       <c r="F167" t="n">
-        <v>77008.66863</v>
+        <v>77008.52419700001</v>
       </c>
       <c r="G167" t="n">
-        <v>98888.44248</v>
+        <v>98888.06174999999</v>
       </c>
       <c r="H167" t="n">
-        <v>134877.1573</v>
+        <v>134876.087526</v>
       </c>
       <c r="I167" t="n">
-        <v>196003.09444</v>
+        <v>195999.08902</v>
       </c>
       <c r="J167" t="n">
         <v>2049133.635555</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1262.088848</v>
+        <v>1262.088773</v>
       </c>
       <c r="F168" t="n">
-        <v>1409.770449</v>
+        <v>1409.770204</v>
       </c>
       <c r="G168" t="n">
-        <v>1936.631109</v>
+        <v>1936.63035</v>
       </c>
       <c r="H168" t="n">
-        <v>2721.687992</v>
+        <v>2721.685675</v>
       </c>
       <c r="I168" t="n">
-        <v>3965.536272</v>
+        <v>3965.527329</v>
       </c>
       <c r="J168" t="n">
         <v>9322.670016</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>791915.410877</v>
+        <v>791915.470864</v>
       </c>
       <c r="F169" t="n">
-        <v>866435.077328</v>
+        <v>866435.242601</v>
       </c>
       <c r="G169" t="n">
-        <v>1169600.283782</v>
+        <v>1169600.735382</v>
       </c>
       <c r="H169" t="n">
-        <v>1678945.962722</v>
+        <v>1678947.269063</v>
       </c>
       <c r="I169" t="n">
-        <v>2574963.587003</v>
+        <v>2574968.603173</v>
       </c>
       <c r="J169" t="n">
         <v>1367429.45446</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>35520.133726</v>
+        <v>35520.135001</v>
       </c>
       <c r="F170" t="n">
-        <v>48834.030385</v>
+        <v>48834.033495</v>
       </c>
       <c r="G170" t="n">
-        <v>78520.946301</v>
+        <v>78520.952892</v>
       </c>
       <c r="H170" t="n">
-        <v>121637.133372</v>
+        <v>121637.147408</v>
       </c>
       <c r="I170" t="n">
-        <v>187729.443514</v>
+        <v>187729.484208</v>
       </c>
       <c r="J170" t="n">
         <v>243814.141347</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>76086.10863800001</v>
+        <v>76086.09723100001</v>
       </c>
       <c r="F171" t="n">
-        <v>80786.298691</v>
+        <v>80786.26501</v>
       </c>
       <c r="G171" t="n">
-        <v>105755.158009</v>
+        <v>105755.062045</v>
       </c>
       <c r="H171" t="n">
-        <v>141658.045532</v>
+        <v>141657.772395</v>
       </c>
       <c r="I171" t="n">
-        <v>196523.999118</v>
+        <v>196523.009519</v>
       </c>
       <c r="J171" t="n">
         <v>669189.073183</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>14666.571202</v>
+        <v>14666.473228</v>
       </c>
       <c r="F172" t="n">
-        <v>15007.96117</v>
+        <v>15007.700453</v>
       </c>
       <c r="G172" t="n">
-        <v>18476.162174</v>
+        <v>18475.512724</v>
       </c>
       <c r="H172" t="n">
-        <v>23727.013197</v>
+        <v>23725.350153</v>
       </c>
       <c r="I172" t="n">
-        <v>33165.315318</v>
+        <v>33159.613581</v>
       </c>
       <c r="J172" t="n">
         <v>2402586.720513</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2839.738237</v>
+        <v>2839.73843</v>
       </c>
       <c r="F173" t="n">
-        <v>3711.337794</v>
+        <v>3711.338394</v>
       </c>
       <c r="G173" t="n">
-        <v>5769.404024</v>
+        <v>5769.405812</v>
       </c>
       <c r="H173" t="n">
-        <v>8775.16426</v>
+        <v>8775.169594999999</v>
       </c>
       <c r="I173" t="n">
-        <v>13572.687717</v>
+        <v>13572.708198</v>
       </c>
       <c r="J173" t="n">
         <v>9729.991878999999</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1004255.762939</v>
+        <v>1004255.783619</v>
       </c>
       <c r="F174" t="n">
-        <v>1017845.646147</v>
+        <v>1017845.693571</v>
       </c>
       <c r="G174" t="n">
-        <v>1281302.184613</v>
+        <v>1281302.294949</v>
       </c>
       <c r="H174" t="n">
-        <v>1694995.325025</v>
+        <v>1694995.591406</v>
       </c>
       <c r="I174" t="n">
-        <v>2375346.167642</v>
+        <v>2375346.989876</v>
       </c>
       <c r="J174" t="n">
         <v>2848011.448481</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5891.636559</v>
+        <v>5891.63709</v>
       </c>
       <c r="F175" t="n">
-        <v>9069.689625999999</v>
+        <v>9069.691607999999</v>
       </c>
       <c r="G175" t="n">
-        <v>16575.683277</v>
+        <v>16575.690292</v>
       </c>
       <c r="H175" t="n">
-        <v>29070.208616</v>
+        <v>29070.23262</v>
       </c>
       <c r="I175" t="n">
-        <v>50855.153826</v>
+        <v>50855.256648</v>
       </c>
       <c r="J175" t="n">
         <v>28123.07751</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>499.791536</v>
+        <v>499.791464</v>
       </c>
       <c r="F176" t="n">
-        <v>478.514447</v>
+        <v>478.514274</v>
       </c>
       <c r="G176" t="n">
-        <v>596.593085</v>
+        <v>596.592639</v>
       </c>
       <c r="H176" t="n">
-        <v>802.324288</v>
+        <v>802.323035</v>
       </c>
       <c r="I176" t="n">
-        <v>1159.405814</v>
+        <v>1159.401029</v>
       </c>
       <c r="J176" t="n">
         <v>3719.860725</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>518228.634516</v>
+        <v>518228.651421</v>
       </c>
       <c r="F177" t="n">
-        <v>721395.109065</v>
+        <v>721395.141998</v>
       </c>
       <c r="G177" t="n">
-        <v>1159769.197007</v>
+        <v>1159769.22634</v>
       </c>
       <c r="H177" t="n">
-        <v>1747278.529338</v>
+        <v>1747278.4644</v>
       </c>
       <c r="I177" t="n">
-        <v>2560152.056256</v>
+        <v>2560151.521345</v>
       </c>
       <c r="J177" t="n">
         <v>3587372.888415</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1257.078176</v>
+        <v>1257.07804</v>
       </c>
       <c r="F178" t="n">
-        <v>1498.874908</v>
+        <v>1498.874442</v>
       </c>
       <c r="G178" t="n">
-        <v>2156.503956</v>
+        <v>2156.50249</v>
       </c>
       <c r="H178" t="n">
-        <v>3168.936126</v>
+        <v>3168.931551</v>
       </c>
       <c r="I178" t="n">
-        <v>4817.235255</v>
+        <v>4817.217115</v>
       </c>
       <c r="J178" t="n">
         <v>15115.034799</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>868.607434</v>
+        <v>868.607346</v>
       </c>
       <c r="F179" t="n">
-        <v>911.106497</v>
+        <v>911.10624</v>
       </c>
       <c r="G179" t="n">
-        <v>1220.983116</v>
+        <v>1220.982352</v>
       </c>
       <c r="H179" t="n">
-        <v>1694.402959</v>
+        <v>1694.400656</v>
       </c>
       <c r="I179" t="n">
-        <v>2461.721937</v>
+        <v>2461.712945</v>
       </c>
       <c r="J179" t="n">
         <v>7453.602513</v>
@@ -14130,19 +14130,19 @@
         </is>
       </c>
       <c r="E181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="F181" t="n">
+        <v>-1e-06</v>
+      </c>
+      <c r="G181" t="n">
         <v>3e-06</v>
       </c>
-      <c r="F181" t="n">
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="n">
         <v>1e-06</v>
-      </c>
-      <c r="G181" t="n">
-        <v>4e-06</v>
-      </c>
-      <c r="H181" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="I181" t="n">
-        <v>-1e-06</v>
       </c>
       <c r="J181" t="n">
         <v>-2e-06</v>
